--- a/results/Int Task Remove ACC 0.2/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC 0.2/Rando_6_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8032382937541875</v>
+        <v>0.7918019057544852</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8014634358172659</v>
+        <v>0.7851844958931984</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7874705327675624</v>
+        <v>0.7836180798530981</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6911573488175885</v>
+        <v>0.7831348172411225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6826410084617485</v>
+        <v>0.7841249162510235</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6737108861262066</v>
+        <v>0.765635003349959</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6737108861262066</v>
+        <v>0.7682653415717511</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6588668453311497</v>
+        <v>0.7836193205786744</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6599884612521403</v>
+        <v>0.7792141244199609</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6490427802178714</v>
+        <v>0.7877614829152089</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6493132583935085</v>
+        <v>0.7974304573314475</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6520397528474652</v>
+        <v>0.7800727065187723</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6362868805677561</v>
+        <v>0.7811943224397628</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6362868805677561</v>
+        <v>0.7820529045385742</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6310379910171469</v>
+        <v>0.7782240254100599</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6390326062681456</v>
+        <v>0.7744453956673862</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6410630536737885</v>
+        <v>0.7747586788754064</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6385375567631951</v>
+        <v>0.7790323581230303</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6367391250403236</v>
+        <v>0.770620859078389</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6257785552991389</v>
+        <v>0.7642354648998735</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6284045509814139</v>
+        <v>0.7654575795925458</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.63000942951438</v>
+        <v>0.7753585696915557</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6600300255589469</v>
+        <v>0.7850083128613613</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6596664929650859</v>
+        <v>0.7684824685476066</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.659302960371225</v>
+        <v>0.7585622472021638</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7074232611231048</v>
+        <v>0.7584617484304821</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6774795900642696</v>
+        <v>0.7659879897764212</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.679278021787141</v>
+        <v>0.7641585399141417</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.680268120797042</v>
+        <v>0.7528536688255292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6741147423012978</v>
+        <v>0.7172411226085015</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6792941512196333</v>
+        <v>0.719685351993846</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6792941512196333</v>
+        <v>0.6728299709670216</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6787221767289511</v>
+        <v>0.7029969726295938</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.627692374500608</v>
+        <v>0.6969248616590983</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6215389960048636</v>
+        <v>0.684498374649495</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.668100325070101</v>
+        <v>0.684498374649495</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6900022333060374</v>
+        <v>0.684498374649495</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6884358172659371</v>
+        <v>0.6728299709670216</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6090814908558525</v>
+        <v>0.6099394525918758</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6048890791334772</v>
+        <v>0.5743076751284151</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6240731779944911</v>
+        <v>0.5734993424154445</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6132013201320132</v>
+        <v>0.56640611429564</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5926089977418795</v>
+        <v>0.5707802923149458</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5777562718677882</v>
+        <v>0.5702114196382044</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5722058860021341</v>
+        <v>0.5665215017742375</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5737723020422343</v>
+        <v>0.5646728206655252</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5571428571428572</v>
+        <v>0.5649861038735452</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5597570659321571</v>
+        <v>0.5686642348445371</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.561122484428894</v>
+        <v>0.5659259534976054</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5549188565473089</v>
+        <v>0.5659259534976054</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4817538896746817</v>
+        <v>0.5659259534976054</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5857924514255937</v>
+        <v>0.5704626665674086</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5565876324474552</v>
+        <v>0.5163161616913571</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.556054120449639</v>
+        <v>0.5221754882255143</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4796409340182138</v>
+        <v>0.5257295466388744</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4465923472046452</v>
+        <v>0.5264876299660041</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3825510558574654</v>
+        <v>0.5165140574207797</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.380577061465545</v>
+        <v>0.4850275441077943</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3484180748901958</v>
+        <v>0.5301155115511551</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.3687448820069977</v>
+        <v>0.5392317427231446</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.3813413484205563</v>
+        <v>0.5682386659718603</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4351851162559865</v>
+        <v>0.4867490508449341</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.3728634705575821</v>
+        <v>0.5263883719198987</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.3697926747561974</v>
+        <v>0.5259125536613811</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.3680252611727338</v>
+        <v>0.5259125536613811</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.3651480185612547</v>
+        <v>0.5264076031663316</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.3052277972158118</v>
+        <v>0.5350244422938535</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.2998870939725551</v>
+        <v>0.5282134792426612</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.3123780987121269</v>
+        <v>0.533829003201072</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.3357397205886002</v>
+        <v>0.5333842030819623</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4143278989553091</v>
+        <v>0.51870703987692</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.3849692300057073</v>
+        <v>0.51870703987692</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4212598327501923</v>
+        <v>0.51870703987692</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4083221668031465</v>
+        <v>0.5183435072830591</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.402285416511576</v>
+        <v>0.5219019082359364</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4396089232983449</v>
+        <v>0.5204167597210849</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.3867217548822551</v>
+        <v>0.5169514131864315</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4549808928261247</v>
+        <v>0.5381765056204869</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4433360629296013</v>
+        <v>0.5406207350058314</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4433360629296013</v>
+        <v>0.5508660264522693</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4448640164768357</v>
+        <v>0.5504212263331596</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.454668850343681</v>
+        <v>0.5277922529095015</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4841218144370828</v>
+        <v>0.5212443236804883</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.520319362763344</v>
+        <v>0.5133235316012804</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5085312290627559</v>
+        <v>0.5093587930221594</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5085312290627559</v>
+        <v>0.5023939799995036</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5077923769820591</v>
+        <v>0.4995551998808904</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5077923769820591</v>
+        <v>0.4995551998808904</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4976860468001687</v>
+        <v>0.4998684830889104</v>
       </c>
     </row>
   </sheetData>
